--- a/config/Excel/Zone_Stage_Drops.xlsx
+++ b/config/Excel/Zone_Stage_Drops.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="關卡掉落" sheetId="1" r:id="Rb4f920c8c3964d6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="關卡掉落" sheetId="1" r:id="Re730e72ff4b14b72"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -153,7 +153,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ZoneStageDropsTable" displayName="ZoneStageDropsTable" ref="A1:I17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ZoneStageDropsTable" displayName="ZoneStageDropsTable" ref="A1:I29" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="地圖識別碼"/>
     <x:tableColumn id="2" name="最低關卡"/>
@@ -868,10 +868,358 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
+    <x:row r="18" ht="15" hidden="0" customHeight="1">
+      <x:c r="A18" s="18" t="str">
+        <x:v>god_battlefield</x:v>
+      </x:c>
+      <x:c r="B18" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C18" s="20" t="str">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="D18" s="18" t="str">
+        <x:v>53|48|47|10|3|1|0.08|0</x:v>
+      </x:c>
+      <x:c r="E18" s="18" t="str">
+        <x:v>11|1.7|0.6|0.1|0.08</x:v>
+      </x:c>
+      <x:c r="F18" s="18" t="str">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G18" s="18" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H18" s="18" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I18" s="18" t="str">
+        <x:v>0.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="15" hidden="0" customHeight="1">
+      <x:c r="A19" s="18" t="str">
+        <x:v>god_battlefield</x:v>
+      </x:c>
+      <x:c r="B19" s="20" t="str">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="C19" s="20" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="D19" s="18" t="str">
+        <x:v>61|51|49|20|6|2|0.16|0</x:v>
+      </x:c>
+      <x:c r="E19" s="18" t="str">
+        <x:v>14|2.4|0.8|0.2|0.16</x:v>
+      </x:c>
+      <x:c r="F19" s="18" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G19" s="18" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H19" s="18" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I19" s="18" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="15" hidden="0" customHeight="1">
+      <x:c r="A20" s="18" t="str">
+        <x:v>god_battlefield</x:v>
+      </x:c>
+      <x:c r="B20" s="20" t="str">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="C20" s="20" t="str">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="D20" s="18" t="str">
+        <x:v>69|54|51|30|9|3|0.24|0</x:v>
+      </x:c>
+      <x:c r="E20" s="18" t="str">
+        <x:v>17|3.1|1|0.3|0.24</x:v>
+      </x:c>
+      <x:c r="F20" s="18" t="str">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G20" s="18" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H20" s="18" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I20" s="18" t="str">
+        <x:v>1.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="15" hidden="0" customHeight="1">
+      <x:c r="A21" s="18" t="str">
+        <x:v>god_battlefield</x:v>
+      </x:c>
+      <x:c r="B21" s="20" t="str">
+        <x:v>451</x:v>
+      </x:c>
+      <x:c r="C21" s="20" t="str">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="D21" s="18" t="str">
+        <x:v>77|57|53|40|12|4|0.32|0</x:v>
+      </x:c>
+      <x:c r="E21" s="18" t="str">
+        <x:v>20|3.8|1.2|0.4|0.32</x:v>
+      </x:c>
+      <x:c r="F21" s="18" t="str">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G21" s="18" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H21" s="18" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I21" s="18" t="str">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="15" hidden="0" customHeight="1">
+      <x:c r="A22" s="18" t="str">
+        <x:v>god_chaos</x:v>
+      </x:c>
+      <x:c r="B22" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C22" s="20" t="str">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="D22" s="18" t="str">
+        <x:v>61|56|55|10|3|1|0.08|0</x:v>
+      </x:c>
+      <x:c r="E22" s="18" t="str">
+        <x:v>11|1.7|0.6|0.1|0.08</x:v>
+      </x:c>
+      <x:c r="F22" s="18" t="str">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G22" s="18" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H22" s="18" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I22" s="18" t="str">
+        <x:v>0.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="15" hidden="0" customHeight="1">
+      <x:c r="A23" s="18" t="str">
+        <x:v>god_chaos</x:v>
+      </x:c>
+      <x:c r="B23" s="20" t="str">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="C23" s="20" t="str">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="D23" s="18" t="str">
+        <x:v>69|59|57|20|6|2|0.16|0</x:v>
+      </x:c>
+      <x:c r="E23" s="18" t="str">
+        <x:v>14|2.4|0.8|0.2|0.16</x:v>
+      </x:c>
+      <x:c r="F23" s="18" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G23" s="18" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H23" s="18" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I23" s="18" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="15" hidden="0" customHeight="1">
+      <x:c r="A24" s="18" t="str">
+        <x:v>god_chaos</x:v>
+      </x:c>
+      <x:c r="B24" s="20" t="str">
+        <x:v>351</x:v>
+      </x:c>
+      <x:c r="C24" s="20" t="str">
+        <x:v>525</x:v>
+      </x:c>
+      <x:c r="D24" s="18" t="str">
+        <x:v>77|62|59|30|9|3|0.24|0</x:v>
+      </x:c>
+      <x:c r="E24" s="18" t="str">
+        <x:v>17|3.1|1|0.3|0.24</x:v>
+      </x:c>
+      <x:c r="F24" s="18" t="str">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G24" s="18" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H24" s="18" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I24" s="18" t="str">
+        <x:v>1.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="15" hidden="0" customHeight="1">
+      <x:c r="A25" s="18" t="str">
+        <x:v>god_chaos</x:v>
+      </x:c>
+      <x:c r="B25" s="20" t="str">
+        <x:v>526</x:v>
+      </x:c>
+      <x:c r="C25" s="20" t="str">
+        <x:v>700</x:v>
+      </x:c>
+      <x:c r="D25" s="18" t="str">
+        <x:v>85|65|61|40|12|4|0.32|0</x:v>
+      </x:c>
+      <x:c r="E25" s="18" t="str">
+        <x:v>20|3.8|1.2|0.4|0.32</x:v>
+      </x:c>
+      <x:c r="F25" s="18" t="str">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G25" s="18" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H25" s="18" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I25" s="18" t="str">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="15" hidden="0" customHeight="1">
+      <x:c r="A26" s="18" t="str">
+        <x:v>god_sanctuary</x:v>
+      </x:c>
+      <x:c r="B26" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C26" s="20" t="str">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="D26" s="18" t="str">
+        <x:v>69|64|63|10|3|1|0.08|0</x:v>
+      </x:c>
+      <x:c r="E26" s="18" t="str">
+        <x:v>11|1.7|0.6|0.1|0.08</x:v>
+      </x:c>
+      <x:c r="F26" s="18" t="str">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G26" s="18" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H26" s="18" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I26" s="18" t="str">
+        <x:v>0.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="15" hidden="0" customHeight="1">
+      <x:c r="A27" s="18" t="str">
+        <x:v>god_sanctuary</x:v>
+      </x:c>
+      <x:c r="B27" s="20" t="str">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="C27" s="20" t="str">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="D27" s="18" t="str">
+        <x:v>77|67|65|20|6|2|0.16|0</x:v>
+      </x:c>
+      <x:c r="E27" s="18" t="str">
+        <x:v>14|2.4|0.8|0.2|0.16</x:v>
+      </x:c>
+      <x:c r="F27" s="18" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G27" s="18" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H27" s="18" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I27" s="18" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="15" hidden="0" customHeight="1">
+      <x:c r="A28" s="18" t="str">
+        <x:v>god_sanctuary</x:v>
+      </x:c>
+      <x:c r="B28" s="20" t="str">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="C28" s="20" t="str">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="D28" s="18" t="str">
+        <x:v>85|70|67|30|9|3|0.24|0</x:v>
+      </x:c>
+      <x:c r="E28" s="18" t="str">
+        <x:v>17|3.1|1|0.3|0.24</x:v>
+      </x:c>
+      <x:c r="F28" s="18" t="str">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G28" s="18" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H28" s="18" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I28" s="18" t="str">
+        <x:v>1.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="15" hidden="0" customHeight="1">
+      <x:c r="A29" s="18" t="str">
+        <x:v>god_sanctuary</x:v>
+      </x:c>
+      <x:c r="B29" s="20" t="str">
+        <x:v>601</x:v>
+      </x:c>
+      <x:c r="C29" s="20" t="str">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c r="D29" s="18" t="str">
+        <x:v>93|73|69|40|12|4|0.32|0</x:v>
+      </x:c>
+      <x:c r="E29" s="18" t="str">
+        <x:v>20|3.8|1.2|0.4|0.32</x:v>
+      </x:c>
+      <x:c r="F29" s="18" t="str">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G29" s="18" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H29" s="18" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I29" s="18" t="str">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc281add2368e431c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f636344bed54727"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/config/Excel/Zone_Stage_Drops.xlsx
+++ b/config/Excel/Zone_Stage_Drops.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="關卡掉落" sheetId="1" r:id="Re730e72ff4b14b72"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="關卡掉落" sheetId="1" r:id="R763e120f171c4e63"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -153,13 +153,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ZoneStageDropsTable" displayName="ZoneStageDropsTable" ref="A1:I29" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ZoneStageDropsTable" displayName="ZoneStageDropsTable" ref="A1:I31" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="地圖識別碼"/>
     <x:tableColumn id="2" name="最低關卡"/>
     <x:tableColumn id="3" name="最高關卡"/>
-    <x:tableColumn id="4" name="裝備掉落率（等級0至7）"/>
-    <x:tableColumn id="5" name="寶石掉落率（等級1至5）"/>
+    <x:tableColumn id="4" name="裝備掉落率（品質R0至R10）"/>
+    <x:tableColumn id="5" name="寶石掉落率（等級R1至R5）"/>
     <x:tableColumn id="6" name="技能書掉落率"/>
     <x:tableColumn id="7" name="太古精華掉落率"/>
     <x:tableColumn id="8" name="魔塵掉落率"/>
@@ -367,7 +367,7 @@
     <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="28" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="32" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="26" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
@@ -375,7 +375,7 @@
     <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="1" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A1" s="14" t="str">
         <x:v>地圖識別碼</x:v>
       </x:c>
@@ -386,10 +386,10 @@
         <x:v>最高關卡</x:v>
       </x:c>
       <x:c r="D1" s="14" t="str">
-        <x:v>裝備掉落率（等級0至7）</x:v>
+        <x:v>裝備掉落率（品質R0至R10）</x:v>
       </x:c>
       <x:c r="E1" s="14" t="str">
-        <x:v>寶石掉落率（等級1至5）</x:v>
+        <x:v>寶石掉落率（等級R1至R5）</x:v>
       </x:c>
       <x:c r="F1" s="14" t="str">
         <x:v>技能書掉落率</x:v>
@@ -415,7 +415,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="D2" s="18" t="str">
-        <x:v>25|15|10|0|0|0|0|0</x:v>
+        <x:v>25|15|10|0|0|0|0|0|0|0|0</x:v>
       </x:c>
       <x:c r="E2" s="18" t="str">
         <x:v>2|0.5|0.2|0|0</x:v>
@@ -444,7 +444,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="D3" s="18" t="str">
-        <x:v>35|20|15|5|1|0|0|0</x:v>
+        <x:v>35|20|15|5|1|0|0|0|0|0|0</x:v>
       </x:c>
       <x:c r="E3" s="18" t="str">
         <x:v>4|0.8|0.3|0|0</x:v>
@@ -473,7 +473,7 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="D4" s="18" t="str">
-        <x:v>40|30|20|10|2.5|1|0|0</x:v>
+        <x:v>40|30|20|10|2.5|1|0|0|0|0|0</x:v>
       </x:c>
       <x:c r="E4" s="18" t="str">
         <x:v>6|1.1|0.4|0|0</x:v>
@@ -502,7 +502,7 @@
         <x:v>200</x:v>
       </x:c>
       <x:c r="D5" s="18" t="str">
-        <x:v>50|40|30|15|5|2|0.05|0</x:v>
+        <x:v>50|40|30|15|5|2|0.05|0|0|0|0</x:v>
       </x:c>
       <x:c r="E5" s="18" t="str">
         <x:v>8|1.4|0.5|0.1|0</x:v>
@@ -531,7 +531,7 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="D6" s="18" t="str">
-        <x:v>30|20|12|1|0|0|0|0</x:v>
+        <x:v>30|20|12|1|0|0|0|0|0|0|0</x:v>
       </x:c>
       <x:c r="E6" s="18" t="str">
         <x:v>3|0.7|0.25|0|0</x:v>
@@ -560,7 +560,7 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="D7" s="18" t="str">
-        <x:v>40|28|18|7|2|0.5|0|0</x:v>
+        <x:v>40|28|18|7|2|0.5|0|0|0|0|0</x:v>
       </x:c>
       <x:c r="E7" s="18" t="str">
         <x:v>5|1|0.4|0|0</x:v>
@@ -589,7 +589,7 @@
         <x:v>225</x:v>
       </x:c>
       <x:c r="D8" s="18" t="str">
-        <x:v>48|36|25|12|4|1.5|0.05|0</x:v>
+        <x:v>48|36|25|12|4|1.5|0.05|0|0|0|0</x:v>
       </x:c>
       <x:c r="E8" s="18" t="str">
         <x:v>7|1.3|0.5|0.1|0</x:v>
@@ -618,7 +618,7 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="D9" s="18" t="str">
-        <x:v>55|45|34|18|6|2.5|0.1|0</x:v>
+        <x:v>55|45|34|18|6|2.5|0.1|0|0|0|0</x:v>
       </x:c>
       <x:c r="E9" s="18" t="str">
         <x:v>9|1.7|0.6|0.2|0</x:v>
@@ -647,7 +647,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="D10" s="18" t="str">
-        <x:v>35|25|15|3|0|0|0|0</x:v>
+        <x:v>35|25|15|3|0|0|0|0|0|0|0</x:v>
       </x:c>
       <x:c r="E10" s="18" t="str">
         <x:v>4|0.8|0.3|0|0</x:v>
@@ -676,7 +676,7 @@
         <x:v>200</x:v>
       </x:c>
       <x:c r="D11" s="18" t="str">
-        <x:v>45|35|23|10|3|1|0|0</x:v>
+        <x:v>45|35|23|10|3|1|0|0|0|0|0</x:v>
       </x:c>
       <x:c r="E11" s="18" t="str">
         <x:v>6|1.1|0.4|0|0</x:v>
@@ -705,7 +705,7 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="D12" s="18" t="str">
-        <x:v>52|42|30|15|5|2|0.1|0</x:v>
+        <x:v>52|42|30|15|5|2|0.1|0|0|0|0</x:v>
       </x:c>
       <x:c r="E12" s="18" t="str">
         <x:v>9|1.7|0.6|0.2|0</x:v>
@@ -734,7 +734,7 @@
         <x:v>400</x:v>
       </x:c>
       <x:c r="D13" s="18" t="str">
-        <x:v>60|50|38|20|8|3.5|0.2|0</x:v>
+        <x:v>60|50|38|20|8|3.5|0.2|0|0|0|0</x:v>
       </x:c>
       <x:c r="E13" s="18" t="str">
         <x:v>12|2|0.7|0.3|0.2</x:v>
@@ -763,7 +763,7 @@
         <x:v>125</x:v>
       </x:c>
       <x:c r="D14" s="18" t="str">
-        <x:v>38|28|18|5|1|0|0|0</x:v>
+        <x:v>38|28|18|5|1|0|0|0|0|0|0</x:v>
       </x:c>
       <x:c r="E14" s="18" t="str">
         <x:v>5|1|0.4|0|0</x:v>
@@ -792,7 +792,7 @@
         <x:v>250</x:v>
       </x:c>
       <x:c r="D15" s="18" t="str">
-        <x:v>48|38|26|12|4|1|0.03|0</x:v>
+        <x:v>48|38|26|12|4|1|0.03|0|0|0|0</x:v>
       </x:c>
       <x:c r="E15" s="18" t="str">
         <x:v>7|1.3|0.5|0.1|0</x:v>
@@ -821,7 +821,7 @@
         <x:v>375</x:v>
       </x:c>
       <x:c r="D16" s="18" t="str">
-        <x:v>58|48|36|18|7|3|0.12|0</x:v>
+        <x:v>58|48|36|18|7|3|0.12|0|0|0|0</x:v>
       </x:c>
       <x:c r="E16" s="18" t="str">
         <x:v>10|1.8|0.65|0.2|0.1</x:v>
@@ -850,7 +850,7 @@
         <x:v>500</x:v>
       </x:c>
       <x:c r="D17" s="18" t="str">
-        <x:v>68|58|45|25|10|4.5|0.25|0</x:v>
+        <x:v>68|58|45|25|10|4.5|0.25|0|0|0|0</x:v>
       </x:c>
       <x:c r="E17" s="18" t="str">
         <x:v>14|2.3|0.8|0.4|0.3</x:v>
@@ -879,7 +879,7 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="D18" s="18" t="str">
-        <x:v>53|48|47|10|3|1|0.08|0</x:v>
+        <x:v>53|48|47|10|3|1|0.08|0|0|0|0</x:v>
       </x:c>
       <x:c r="E18" s="18" t="str">
         <x:v>11|1.7|0.6|0.1|0.08</x:v>
@@ -908,7 +908,7 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="D19" s="18" t="str">
-        <x:v>61|51|49|20|6|2|0.16|0</x:v>
+        <x:v>61|51|49|20|6|2|0.16|0|0|0|0</x:v>
       </x:c>
       <x:c r="E19" s="18" t="str">
         <x:v>14|2.4|0.8|0.2|0.16</x:v>
@@ -937,7 +937,7 @@
         <x:v>450</x:v>
       </x:c>
       <x:c r="D20" s="18" t="str">
-        <x:v>69|54|51|30|9|3|0.24|0</x:v>
+        <x:v>69|54|51|30|9|3|0.24|0|0|0|0</x:v>
       </x:c>
       <x:c r="E20" s="18" t="str">
         <x:v>17|3.1|1|0.3|0.24</x:v>
@@ -963,10 +963,10 @@
         <x:v>451</x:v>
       </x:c>
       <x:c r="C21" s="20" t="str">
-        <x:v>600</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="D21" s="18" t="str">
-        <x:v>77|57|53|40|12|4|0.32|0</x:v>
+        <x:v>77|57|53|40|12|4|0.32|0|0|0|0</x:v>
       </x:c>
       <x:c r="E21" s="18" t="str">
         <x:v>20|3.8|1.2|0.4|0.32</x:v>
@@ -986,31 +986,31 @@
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
       <x:c r="A22" s="18" t="str">
-        <x:v>god_chaos</x:v>
+        <x:v>god_battlefield</x:v>
       </x:c>
       <x:c r="B22" s="20" t="str">
-        <x:v>1</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="C22" s="20" t="str">
-        <x:v>175</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="D22" s="18" t="str">
-        <x:v>61|56|55|10|3|1|0.08|0</x:v>
+        <x:v>77|57|53|40|12|4|0.32|0|0|1|0</x:v>
       </x:c>
       <x:c r="E22" s="18" t="str">
-        <x:v>11|1.7|0.6|0.1|0.08</x:v>
+        <x:v>20|3.8|1.2|0.4|0.32</x:v>
       </x:c>
       <x:c r="F22" s="18" t="str">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G22" s="18" t="str">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H22" s="18" t="str">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I22" s="18" t="str">
-        <x:v>0.5</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
@@ -1018,28 +1018,28 @@
         <x:v>god_chaos</x:v>
       </x:c>
       <x:c r="B23" s="20" t="str">
-        <x:v>176</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C23" s="20" t="str">
-        <x:v>350</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="D23" s="18" t="str">
-        <x:v>69|59|57|20|6|2|0.16|0</x:v>
+        <x:v>61|56|55|10|3|1|0.08|0|0|0|0</x:v>
       </x:c>
       <x:c r="E23" s="18" t="str">
-        <x:v>14|2.4|0.8|0.2|0.16</x:v>
+        <x:v>11|1.7|0.6|0.1|0.08</x:v>
       </x:c>
       <x:c r="F23" s="18" t="str">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G23" s="18" t="str">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H23" s="18" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I23" s="18" t="str">
-        <x:v>1</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
@@ -1047,28 +1047,28 @@
         <x:v>god_chaos</x:v>
       </x:c>
       <x:c r="B24" s="20" t="str">
-        <x:v>351</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C24" s="20" t="str">
-        <x:v>525</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="D24" s="18" t="str">
-        <x:v>77|62|59|30|9|3|0.24|0</x:v>
+        <x:v>69|59|57|20|6|2|0.16|0|0|0|0</x:v>
       </x:c>
       <x:c r="E24" s="18" t="str">
-        <x:v>17|3.1|1|0.3|0.24</x:v>
+        <x:v>14|2.4|0.8|0.2|0.16</x:v>
       </x:c>
       <x:c r="F24" s="18" t="str">
-        <x:v>11</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G24" s="18" t="str">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H24" s="18" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I24" s="18" t="str">
-        <x:v>1.5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="15" hidden="0" customHeight="1">
@@ -1076,86 +1076,86 @@
         <x:v>god_chaos</x:v>
       </x:c>
       <x:c r="B25" s="20" t="str">
-        <x:v>526</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="C25" s="20" t="str">
-        <x:v>700</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="D25" s="18" t="str">
-        <x:v>85|65|61|40|12|4|0.32|0</x:v>
+        <x:v>77|62|59|30|9|3|0.24|0|0|0|0</x:v>
       </x:c>
       <x:c r="E25" s="18" t="str">
-        <x:v>20|3.8|1.2|0.4|0.32</x:v>
+        <x:v>17|3.1|1|0.3|0.24</x:v>
       </x:c>
       <x:c r="F25" s="18" t="str">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G25" s="18" t="str">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H25" s="18" t="str">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="I25" s="18" t="str">
-        <x:v>2</x:v>
+        <x:v>1.5</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="15" hidden="0" customHeight="1">
       <x:c r="A26" s="18" t="str">
-        <x:v>god_sanctuary</x:v>
+        <x:v>god_chaos</x:v>
       </x:c>
       <x:c r="B26" s="20" t="str">
-        <x:v>1</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="C26" s="20" t="str">
-        <x:v>200</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="D26" s="18" t="str">
-        <x:v>69|64|63|10|3|1|0.08|0</x:v>
+        <x:v>85|65|61|40|12|4|0.32|0|0|0|0</x:v>
       </x:c>
       <x:c r="E26" s="18" t="str">
-        <x:v>11|1.7|0.6|0.1|0.08</x:v>
+        <x:v>20|3.8|1.2|0.4|0.32</x:v>
       </x:c>
       <x:c r="F26" s="18" t="str">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G26" s="18" t="str">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H26" s="18" t="str">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I26" s="18" t="str">
-        <x:v>0.5</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
       <x:c r="A27" s="18" t="str">
-        <x:v>god_sanctuary</x:v>
+        <x:v>god_chaos</x:v>
       </x:c>
       <x:c r="B27" s="20" t="str">
-        <x:v>201</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="C27" s="20" t="str">
-        <x:v>400</x:v>
+        <x:v>700</x:v>
       </x:c>
       <x:c r="D27" s="18" t="str">
-        <x:v>77|67|65|20|6|2|0.16|0</x:v>
+        <x:v>85|65|61|40|12|4|0.32|0|0|1|0</x:v>
       </x:c>
       <x:c r="E27" s="18" t="str">
-        <x:v>14|2.4|0.8|0.2|0.16</x:v>
+        <x:v>20|3.8|1.2|0.4|0.32</x:v>
       </x:c>
       <x:c r="F27" s="18" t="str">
-        <x:v>9</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G27" s="18" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H27" s="18" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H27" s="18" t="str">
-        <x:v>2</x:v>
-      </x:c>
       <x:c r="I27" s="18" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="15" hidden="0" customHeight="1">
@@ -1163,28 +1163,28 @@
         <x:v>god_sanctuary</x:v>
       </x:c>
       <x:c r="B28" s="20" t="str">
-        <x:v>401</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C28" s="20" t="str">
-        <x:v>600</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="D28" s="18" t="str">
-        <x:v>85|70|67|30|9|3|0.24|0</x:v>
+        <x:v>69|64|63|10|3|1|0.08|0|0|0|0</x:v>
       </x:c>
       <x:c r="E28" s="18" t="str">
-        <x:v>17|3.1|1|0.3|0.24</x:v>
+        <x:v>11|1.7|0.6|0.1|0.08</x:v>
       </x:c>
       <x:c r="F28" s="18" t="str">
-        <x:v>11</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G28" s="18" t="str">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H28" s="18" t="str">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I28" s="18" t="str">
-        <x:v>1.5</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="15" hidden="0" customHeight="1">
@@ -1192,34 +1192,92 @@
         <x:v>god_sanctuary</x:v>
       </x:c>
       <x:c r="B29" s="20" t="str">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="C29" s="20" t="str">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="D29" s="18" t="str">
+        <x:v>77|67|65|20|6|2|0.16|0|0|0|0</x:v>
+      </x:c>
+      <x:c r="E29" s="18" t="str">
+        <x:v>14|2.4|0.8|0.2|0.16</x:v>
+      </x:c>
+      <x:c r="F29" s="18" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G29" s="18" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H29" s="18" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I29" s="18" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="15" hidden="0" customHeight="1">
+      <x:c r="A30" s="18" t="str">
+        <x:v>god_sanctuary</x:v>
+      </x:c>
+      <x:c r="B30" s="20" t="str">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="C30" s="20" t="str">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="D30" s="18" t="str">
+        <x:v>85|70|67|30|9|3|0.24|0|0|0|0</x:v>
+      </x:c>
+      <x:c r="E30" s="18" t="str">
+        <x:v>17|3.1|1|0.3|0.24</x:v>
+      </x:c>
+      <x:c r="F30" s="18" t="str">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G30" s="18" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H30" s="18" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I30" s="18" t="str">
+        <x:v>1.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="15" hidden="0" customHeight="1">
+      <x:c r="A31" s="18" t="str">
+        <x:v>god_sanctuary</x:v>
+      </x:c>
+      <x:c r="B31" s="20" t="str">
         <x:v>601</x:v>
       </x:c>
-      <x:c r="C29" s="20" t="str">
+      <x:c r="C31" s="20" t="str">
         <x:v>800</x:v>
       </x:c>
-      <x:c r="D29" s="18" t="str">
-        <x:v>93|73|69|40|12|4|0.32|0</x:v>
-      </x:c>
-      <x:c r="E29" s="18" t="str">
+      <x:c r="D31" s="18" t="str">
+        <x:v>93|73|69|40|12|4|0.32|0|0|1|0</x:v>
+      </x:c>
+      <x:c r="E31" s="18" t="str">
         <x:v>20|3.8|1.2|0.4|0.32</x:v>
       </x:c>
-      <x:c r="F29" s="18" t="str">
+      <x:c r="F31" s="18" t="str">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="G29" s="18" t="str">
+      <x:c r="G31" s="18" t="str">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H29" s="18" t="str">
+      <x:c r="H31" s="18" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I29" s="18" t="str">
+      <x:c r="I31" s="18" t="str">
         <x:v>2</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f636344bed54727"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d543bb157ce4126"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/config/Excel/Zone_Stage_Drops.xlsx
+++ b/config/Excel/Zone_Stage_Drops.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="關卡掉落" sheetId="1" r:id="R763e120f171c4e63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="關卡掉落" sheetId="1" r:id="R9aacdeabc78d4474"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1277,7 +1277,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d543bb157ce4126"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29694e5a7d4d4db2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/config/Excel/Zone_Stage_Drops.xlsx
+++ b/config/Excel/Zone_Stage_Drops.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E4A0BD1-E8B3-493D-AF92-448C3DC6DA19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1E9EA24-A072-4931-B2BD-56D1E6394D79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -145,10 +145,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>40|30|20|10|0|0|0|0|0|0|0</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>0|0|0|0|2|0|0|0|0|0|0</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -234,6 +230,10 @@
   </si>
   <si>
     <t>93|73|69|40|12|4|0.32|2|0|1|0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>40|30|20|10|1.5|0|0|0|0|0|0</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -678,10 +678,10 @@
         <v>149</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F4" s="5">
         <v>1</v>
@@ -704,10 +704,10 @@
         <v>200</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F5" s="5">
         <v>2</v>
@@ -730,10 +730,10 @@
         <v>49</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F6" s="2">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>35</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F7" s="2">
         <v>0</v>
@@ -782,7 +782,7 @@
         <v>199</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>11</v>
@@ -808,10 +808,10 @@
         <v>249</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F9" s="2">
         <v>2</v>
@@ -834,10 +834,10 @@
         <v>300</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F10" s="2">
         <v>2</v>
@@ -860,7 +860,7 @@
         <v>199</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>11</v>
@@ -886,10 +886,10 @@
         <v>249</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F12" s="2">
         <v>2</v>
@@ -912,10 +912,10 @@
         <v>349</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F13" s="2">
         <v>3</v>
@@ -938,7 +938,7 @@
         <v>400</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>14</v>
@@ -964,7 +964,7 @@
         <v>199</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>11</v>
@@ -990,10 +990,10 @@
         <v>299</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F16" s="2">
         <v>2</v>
@@ -1016,10 +1016,10 @@
         <v>399</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F17" s="2">
         <v>3</v>
@@ -1042,7 +1042,7 @@
         <v>449</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>14</v>
@@ -1068,10 +1068,10 @@
         <v>500</v>
       </c>
       <c r="D19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="F19" s="2">
         <v>4</v>
@@ -1198,7 +1198,7 @@
         <v>600</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>24</v>
@@ -1328,7 +1328,7 @@
         <v>700</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>24</v>
@@ -1432,7 +1432,7 @@
         <v>800</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>24</v>

--- a/config/Excel/Zone_Stage_Drops.xlsx
+++ b/config/Excel/Zone_Stage_Drops.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\claude\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1E9EA24-A072-4931-B2BD-56D1E6394D79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{511087D1-7CAE-405B-BED3-94CF214B6B1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,9 +59,6 @@
     <t>魔塵掉落率</t>
   </si>
   <si>
-    <t>plains</t>
-  </si>
-  <si>
     <t>25|15|10|0|0|0|0|0|0|0|0</t>
   </si>
   <si>
@@ -235,6 +232,9 @@
   <si>
     <t>40|30|20|10|1.5|0|0|0|0|0|0</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icefield</t>
   </si>
 </sst>
 </file>
@@ -617,7 +617,7 @@
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
@@ -626,10 +626,10 @@
         <v>20</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="F2" s="2">
         <v>0</v>
@@ -643,7 +643,7 @@
     </row>
     <row r="3" spans="1:8" ht="15" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B3" s="3">
         <v>21</v>
@@ -652,10 +652,10 @@
         <v>99</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" s="2">
         <v>1</v>
@@ -669,7 +669,7 @@
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B4" s="4">
         <v>100</v>
@@ -678,10 +678,10 @@
         <v>149</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F4" s="5">
         <v>1</v>
@@ -695,7 +695,7 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B5" s="4">
         <v>150</v>
@@ -704,10 +704,10 @@
         <v>200</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F5" s="5">
         <v>2</v>
@@ -721,7 +721,7 @@
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B6" s="3">
         <v>40</v>
@@ -730,10 +730,10 @@
         <v>49</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F6" s="2">
         <v>0</v>
@@ -747,7 +747,7 @@
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B7" s="3">
         <v>50</v>
@@ -756,10 +756,10 @@
         <v>99</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F7" s="2">
         <v>0</v>
@@ -773,7 +773,7 @@
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
@@ -782,10 +782,10 @@
         <v>199</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F8" s="2">
         <v>1</v>
@@ -799,7 +799,7 @@
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="B9" s="3">
         <v>200</v>
@@ -808,10 +808,10 @@
         <v>249</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F9" s="2">
         <v>2</v>
@@ -825,7 +825,7 @@
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="B10" s="3">
         <v>250</v>
@@ -834,10 +834,10 @@
         <v>300</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F10" s="2">
         <v>2</v>
@@ -851,7 +851,7 @@
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" s="3">
         <v>1</v>
@@ -860,10 +860,10 @@
         <v>199</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F11" s="2">
         <v>1</v>
@@ -877,7 +877,7 @@
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" s="3">
         <v>200</v>
@@ -886,10 +886,10 @@
         <v>249</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F12" s="2">
         <v>2</v>
@@ -903,7 +903,7 @@
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="3">
         <v>250</v>
@@ -912,10 +912,10 @@
         <v>349</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F13" s="2">
         <v>3</v>
@@ -929,7 +929,7 @@
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="3">
         <v>350</v>
@@ -938,10 +938,10 @@
         <v>400</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F14" s="2">
         <v>4</v>
@@ -955,7 +955,7 @@
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" s="3">
         <v>1</v>
@@ -964,10 +964,10 @@
         <v>199</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F15" s="2">
         <v>1</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="3">
         <v>200</v>
@@ -990,10 +990,10 @@
         <v>299</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F16" s="2">
         <v>2</v>
@@ -1007,7 +1007,7 @@
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B17" s="3">
         <v>300</v>
@@ -1016,10 +1016,10 @@
         <v>399</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F17" s="2">
         <v>3</v>
@@ -1033,7 +1033,7 @@
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B18" s="3">
         <v>400</v>
@@ -1042,10 +1042,10 @@
         <v>449</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F18" s="2">
         <v>4</v>
@@ -1059,7 +1059,7 @@
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B19" s="3">
         <v>450</v>
@@ -1068,10 +1068,10 @@
         <v>500</v>
       </c>
       <c r="D19" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="F19" s="2">
         <v>4</v>
@@ -1085,7 +1085,7 @@
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1">
       <c r="A20" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B20" s="7">
         <v>1</v>
@@ -1094,10 +1094,10 @@
         <v>150</v>
       </c>
       <c r="D20" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="6" t="s">
         <v>17</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>18</v>
       </c>
       <c r="F20" s="6">
         <v>7</v>
@@ -1111,7 +1111,7 @@
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1">
       <c r="A21" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B21" s="7">
         <v>151</v>
@@ -1120,10 +1120,10 @@
         <v>300</v>
       </c>
       <c r="D21" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>20</v>
       </c>
       <c r="F21" s="6">
         <v>9</v>
@@ -1137,7 +1137,7 @@
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1">
       <c r="A22" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B22" s="7">
         <v>301</v>
@@ -1146,10 +1146,10 @@
         <v>450</v>
       </c>
       <c r="D22" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="6" t="s">
         <v>21</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>22</v>
       </c>
       <c r="F22" s="6">
         <v>11</v>
@@ -1163,7 +1163,7 @@
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1">
       <c r="A23" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B23" s="7">
         <v>451</v>
@@ -1172,10 +1172,10 @@
         <v>550</v>
       </c>
       <c r="D23" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" s="6" t="s">
         <v>23</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="F23" s="6">
         <v>13</v>
@@ -1189,7 +1189,7 @@
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1">
       <c r="A24" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B24" s="7">
         <v>551</v>
@@ -1198,10 +1198,10 @@
         <v>600</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F24" s="6">
         <v>13</v>
@@ -1215,7 +1215,7 @@
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1">
       <c r="A25" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" s="7">
         <v>1</v>
@@ -1224,10 +1224,10 @@
         <v>175</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F25" s="6">
         <v>7</v>
@@ -1241,7 +1241,7 @@
     </row>
     <row r="26" spans="1:8" ht="15" customHeight="1">
       <c r="A26" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" s="7">
         <v>176</v>
@@ -1250,10 +1250,10 @@
         <v>350</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F26" s="6">
         <v>9</v>
@@ -1267,7 +1267,7 @@
     </row>
     <row r="27" spans="1:8" ht="15" customHeight="1">
       <c r="A27" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B27" s="7">
         <v>351</v>
@@ -1276,10 +1276,10 @@
         <v>525</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F27" s="6">
         <v>11</v>
@@ -1293,7 +1293,7 @@
     </row>
     <row r="28" spans="1:8" ht="15" customHeight="1">
       <c r="A28" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B28" s="7">
         <v>526</v>
@@ -1302,10 +1302,10 @@
         <v>550</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F28" s="6">
         <v>13</v>
@@ -1319,7 +1319,7 @@
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1">
       <c r="A29" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B29" s="7">
         <v>551</v>
@@ -1328,10 +1328,10 @@
         <v>700</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F29" s="6">
         <v>13</v>
@@ -1345,7 +1345,7 @@
     </row>
     <row r="30" spans="1:8" ht="15" customHeight="1">
       <c r="A30" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B30" s="7">
         <v>1</v>
@@ -1354,10 +1354,10 @@
         <v>200</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F30" s="6">
         <v>7</v>
@@ -1371,7 +1371,7 @@
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1">
       <c r="A31" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" s="7">
         <v>201</v>
@@ -1380,10 +1380,10 @@
         <v>400</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F31" s="6">
         <v>9</v>
@@ -1397,7 +1397,7 @@
     </row>
     <row r="32" spans="1:8" ht="15" customHeight="1">
       <c r="A32" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B32" s="7">
         <v>401</v>
@@ -1406,10 +1406,10 @@
         <v>600</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F32" s="6">
         <v>11</v>
@@ -1423,7 +1423,7 @@
     </row>
     <row r="33" spans="1:8" ht="15" customHeight="1">
       <c r="A33" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B33" s="7">
         <v>601</v>
@@ -1432,10 +1432,10 @@
         <v>800</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F33" s="6">
         <v>13</v>

--- a/config/Excel/Zone_Stage_Drops.xlsx
+++ b/config/Excel/Zone_Stage_Drops.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\claude\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{511087D1-7CAE-405B-BED3-94CF214B6B1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75A0B4CF-28AF-433C-BC8B-7CED8B71F645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -206,14 +206,6 @@
     <t>12|2|1|0.6|0.1</t>
   </si>
   <si>
-    <t>50|40|30|15|10|3|0.3|0.2|0|0|0</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>50|40|30|15|10|3|0.5|0.3|0|0|0</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>14|3|1|0.4|0.25</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -235,6 +227,14 @@
   </si>
   <si>
     <t>Icefield</t>
+  </si>
+  <si>
+    <t>50|40|30|15|10|3|0.3|0.1|0|0|0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>50|40|30|15|10|3|0.2|0|0|0|0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -678,7 +678,7 @@
         <v>149</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>37</v>
@@ -773,7 +773,7 @@
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
@@ -799,7 +799,7 @@
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B9" s="3">
         <v>200</v>
@@ -825,7 +825,7 @@
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B10" s="3">
         <v>250</v>
@@ -1016,7 +1016,7 @@
         <v>399</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>51</v>
@@ -1042,7 +1042,7 @@
         <v>449</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>13</v>
@@ -1068,10 +1068,10 @@
         <v>500</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F19" s="2">
         <v>4</v>
@@ -1198,7 +1198,7 @@
         <v>600</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>23</v>
@@ -1328,7 +1328,7 @@
         <v>700</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>23</v>
@@ -1432,7 +1432,7 @@
         <v>800</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>23</v>
